--- a/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,27</t>
+          <t>-0,07; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,74</t>
+          <t>-0,56; 4,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,14</t>
+          <t>-0,18; 2,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,57</t>
+          <t>-1,38; 2,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-47,74; 692,07</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-53,19; 764,18</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 181,93</t>
+          <t>-45,66; 184,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,21</t>
+          <t>-1,58; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,15</t>
+          <t>-4,18; -0,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,31</t>
+          <t>-1,2; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,26</t>
+          <t>-1,09; 2,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,68</t>
+          <t>-100,0; 53,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 982,42</t>
+          <t>-100,0; 902,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 266,44</t>
+          <t>-46,69; 295,24</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,33</t>
+          <t>-0,51; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,63</t>
+          <t>-3,47; 0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,11</t>
+          <t>-1,1; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,34</t>
+          <t>-1,06; 3,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,27</t>
+          <t>-100,0; 75,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 638,45</t>
+          <t>-58,03; 613,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,67</t>
+          <t>-0,5; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,64</t>
+          <t>0,04; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,97</t>
+          <t>0,02; 1,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 57,81</t>
+          <t>-0,06; 50,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 273,69</t>
+          <t>-42,12; 278,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 332,28</t>
+          <t>-2,88; 350,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 602,52</t>
+          <t>-17,52; 566,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4794,9</t>
+          <t>-3,21; 3822,9</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,71</t>
+          <t>-1,56; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,0</t>
+          <t>0,01; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,82</t>
+          <t>-0,78; 2,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,51</t>
+          <t>-2,02; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 448,87</t>
+          <t>-6,83; 496,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 253,61</t>
+          <t>-36,56; 215,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 96,98</t>
+          <t>-52,7; 90,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,58</t>
+          <t>-3,55; 0,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,04</t>
+          <t>-5,74; 0,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,93</t>
+          <t>-2,73; 0,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,69</t>
+          <t>-3,68; 2,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 72,48</t>
+          <t>-81,32; 51,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 7,52</t>
+          <t>-79,3; 13,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,01; 152,76</t>
+          <t>-77,73; 136,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 210,45</t>
+          <t>-58,09; 180,92</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,8</t>
+          <t>-0,28; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,99</t>
+          <t>-0,49; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,3</t>
+          <t>0,13; 1,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 22,87</t>
+          <t>0,44; 23,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 117,27</t>
+          <t>-25,97; 112,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 64,96</t>
+          <t>-21,43; 61,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,29; 185,11</t>
+          <t>9,55; 177,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,31; 1165,73</t>
+          <t>20,25; 1210,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,53</t>
+          <t>-0,08; 3,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,02</t>
+          <t>-0,43; 4,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,35</t>
+          <t>-0,23; 2,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,43</t>
+          <t>-1,73; 1,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 692,07</t>
+          <t>-40,32; 881,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 184,58</t>
+          <t>-54,2; 121,99</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,18</t>
+          <t>-1,7; 1,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; -0,04</t>
+          <t>-4,47; -0,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,37</t>
+          <t>-1,02; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,34</t>
+          <t>-0,87; 2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,71</t>
+          <t>-100,0; 32,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 902,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 295,24</t>
+          <t>-39,04; 315,2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,51</t>
+          <t>-0,55; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,51</t>
+          <t>-3,53; 0,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,28</t>
+          <t>-1,11; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,14</t>
+          <t>-1,93; 2,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,54</t>
+          <t>-100,0; 46,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 613,72</t>
+          <t>-76,88; 206,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,89</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1044,16%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,64</t>
+          <t>-0,46; 1,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,68</t>
+          <t>0,01; 2,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,88</t>
+          <t>0,09; 1,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 50,63</t>
+          <t>-0,69; 1,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 278,29</t>
+          <t>-45,05; 299,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 350,62</t>
+          <t>-8,27; 356,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 566,94</t>
+          <t>-0,56; 628,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3822,9</t>
+          <t>-29,51; 120,21</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,33%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,69</t>
+          <t>-1,75; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,32</t>
+          <t>0,06; 3,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,57</t>
+          <t>-0,62; 2,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,53</t>
+          <t>-1,3; 1,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 496,45</t>
+          <t>-6,94; 394,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 215,65</t>
+          <t>-26,66; 274,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 90,08</t>
+          <t>-35,7; 140,63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>-20,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,43</t>
+          <t>-3,56; 0,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 0,18</t>
+          <t>-5,97; 0,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,92</t>
+          <t>-2,8; 0,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,58</t>
+          <t>-5,6; 2,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,32; 51,28</t>
+          <t>-79,82; 76,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 13,03</t>
+          <t>-81,56; 4,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,73; 136,91</t>
+          <t>-74,83; 187,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 180,92</t>
+          <t>-65,3; 103,24</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>309,26%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,75</t>
+          <t>-0,31; 0,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,93</t>
+          <t>-0,52; 0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,14; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 23,57</t>
+          <t>-0,09; 1,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 112,89</t>
+          <t>-25,7; 103,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 61,01</t>
+          <t>-23,32; 62,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 177,06</t>
+          <t>8,96; 183,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,25; 1210,17</t>
+          <t>-3,53; 66,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
